--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
   <si>
     <t/>
   </si>
   <si>
-    <t>20129966</t>
-  </si>
-  <si>
-    <t>N/P MNM LIME 330 ML</t>
+    <t>10011020</t>
+  </si>
+  <si>
+    <t>SIMBA CRL C PTH 34 G</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,55 +28,52 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20070569</t>
+  </si>
+  <si>
+    <t>INDOMLK BANANA 180 G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20142495</t>
-  </si>
-  <si>
-    <t>IDM AIR MINE BTL 1 L</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20045674</t>
-  </si>
-  <si>
-    <t>G/DAY F.MCACN 250 ML</t>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STW TP 225 ML</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20076770</t>
-  </si>
-  <si>
-    <t>G/DAY CAPPCIN 250 ML</t>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG CKT TP 225 ML</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10007970</t>
-  </si>
-  <si>
-    <t>BUAVITA JAMBU 245 ML</t>
+    <t>20034077</t>
+  </si>
+  <si>
+    <t>F/FLAG FCM TP 225 ML</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>10007973</t>
-  </si>
-  <si>
-    <t>BUAVITA MGGA 245 ML</t>
+    <t>20090527</t>
+  </si>
+  <si>
+    <t>CRYSTLN AIR B 600 ML</t>
   </si>
   <si>
     <t>6</t>
@@ -558,15 +555,15 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -575,18 +572,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -595,18 +592,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -615,10 +612,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU1AMKT.xlsx
+++ b/E/DU1AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="21">
   <si>
     <t/>
   </si>
   <si>
-    <t>10011020</t>
-  </si>
-  <si>
-    <t>SIMBA CRL C PTH 34 G</t>
+    <t>20045610</t>
+  </si>
+  <si>
+    <t>SEDAP STO CUP 81 G</t>
   </si>
   <si>
     <t>DU1AMKT</t>
@@ -28,43 +28,40 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20052391</t>
+  </si>
+  <si>
+    <t>SEDAP KR SPS C 81 G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20034078</t>
+  </si>
+  <si>
+    <t>F/FLAG STW TP 225 ML</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>20034079</t>
+  </si>
+  <si>
+    <t>F/FLAG CKT TP 225 ML</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>20070569</t>
   </si>
   <si>
     <t>INDOMLK BANANA 180 G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20034078</t>
-  </si>
-  <si>
-    <t>F/FLAG STW TP 225 ML</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>20034079</t>
-  </si>
-  <si>
-    <t>F/FLAG CKT TP 225 ML</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>20034077</t>
-  </si>
-  <si>
-    <t>F/FLAG FCM TP 225 ML</t>
   </si>
   <si>
     <t>5</t>
@@ -535,15 +532,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -552,18 +549,18 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
@@ -572,18 +569,18 @@
         <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -592,18 +589,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -612,10 +609,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
